--- a/output/pdf_financials_xlsx/MN.xlsx
+++ b/output/pdf_financials_xlsx/MN.xlsx
@@ -1389,19 +1389,19 @@
         </is>
       </c>
       <c r="N16" s="3" t="n">
-        <v>4.880829</v>
+        <v>-4.880829</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>4.274412</v>
+        <v>-4.274412</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>2.833259</v>
+        <v>-2.833259</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>2.284301</v>
+        <v>-2.284301</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>1.566113</v>
+        <v>-1.566113</v>
       </c>
     </row>
     <row r="17">
@@ -1697,19 +1697,19 @@
         </is>
       </c>
       <c r="N20" s="3" t="n">
-        <v>4.880829</v>
+        <v>-4.880829</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>4.274412</v>
+        <v>-4.274412</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>2.833259</v>
+        <v>-2.833259</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>2.284301</v>
+        <v>-2.284301</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>1.566113</v>
+        <v>-1.566113</v>
       </c>
     </row>
     <row r="21">
@@ -1879,19 +1879,19 @@
         </is>
       </c>
       <c r="N23" s="3" t="n">
-        <v>4.880829</v>
+        <v>-4.880829</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>4.274412</v>
+        <v>-4.274412</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>2.833259</v>
+        <v>-2.833259</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>2.284301</v>
+        <v>-2.284301</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>1.566113</v>
+        <v>-1.566113</v>
       </c>
     </row>
     <row r="24">
@@ -2191,19 +2191,19 @@
         </is>
       </c>
       <c r="N27" s="3" t="n">
-        <v>4.880829</v>
+        <v>-4.880829</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>4.274412</v>
+        <v>-4.274412</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>2.833259</v>
+        <v>-2.833259</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>2.284301</v>
+        <v>-2.284301</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>1.566113</v>
+        <v>-1.566113</v>
       </c>
     </row>
     <row r="28">
@@ -2315,19 +2315,19 @@
         </is>
       </c>
       <c r="N29" s="3" t="n">
-        <v>4.880829</v>
+        <v>-4.880829</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>4.274412</v>
+        <v>-4.274412</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>2.833259</v>
+        <v>-2.833259</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>2.284301</v>
+        <v>-2.284301</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>1.566113</v>
+        <v>-1.566113</v>
       </c>
     </row>
     <row r="30">
@@ -2473,19 +2473,19 @@
         </is>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -6076,37 +6076,37 @@
         <v>0.664709</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.447898</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.000198</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.0005509999999999999</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.000802</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.000645</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.000356</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>6.47849</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>9.128221</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>8.875152999999999</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>7.20541</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>5.329324</v>
       </c>
     </row>
     <row r="93">
@@ -9840,7 +9840,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -12832,7 +12836,11 @@
           <t>Reserves 3 790 574 3</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -14648,7 +14656,11 @@
           <t>Reserves 3 356 645 3</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -15967,7 +15979,11 @@
           <t>Reserves 3 520 802 3</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -17682,7 +17698,11 @@
           <t>Reserves 3 476 551 2</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -19282,7 +19302,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -47863,13 +47887,13 @@
         </is>
       </c>
       <c r="S390" s="5" t="n">
-        <v>2.833259</v>
+        <v>-2.833259</v>
       </c>
       <c r="T390" s="5" t="n">
-        <v>2.284301</v>
+        <v>-2.284301</v>
       </c>
       <c r="U390" s="5" t="n">
-        <v>1.566113</v>
+        <v>-1.566113</v>
       </c>
     </row>
     <row r="391">
@@ -49039,13 +49063,13 @@
         </is>
       </c>
       <c r="Q402" s="5" t="n">
-        <v>4.880829</v>
+        <v>-4.880829</v>
       </c>
       <c r="R402" s="5" t="n">
-        <v>4.274412</v>
+        <v>-4.274412</v>
       </c>
       <c r="S402" s="5" t="n">
-        <v>2.833259</v>
+        <v>-2.833259</v>
       </c>
       <c r="T402" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/MN.xlsx
+++ b/output/pdf_financials_xlsx/MN.xlsx
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.002786</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.00167</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -2147,10 +2147,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.067771</v>
+        <v>-0.07055699999999999</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.566088</v>
+        <v>-0.567758</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-2.376518</v>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.067771</v>
+        <v>-0.07055699999999999</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.5554</v>
+        <v>-0.55707</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-2.359562</v>
@@ -2609,7 +2609,7 @@
         <v>0.004191</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.001481</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0</v>
@@ -2725,7 +2725,7 @@
         <v>0.004191</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.001481</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0</v>
@@ -3421,7 +3421,7 @@
         <v>0.110822</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.017374</v>
+        <v>0.015893</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.008193000000000001</v>
@@ -20413,7 +20413,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -62128,7 +62128,7 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E533" s="5" t="n">

--- a/output/pdf_financials_xlsx/MN.xlsx
+++ b/output/pdf_financials_xlsx/MN.xlsx
@@ -2219,7 +2219,7 @@
         <v>0.010688</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.016956</v>
+        <v>0.017408</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>0.019061</v>
@@ -2277,7 +2277,7 @@
         <v>-0.55707</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.359562</v>
+        <v>-2.35911</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-2.986612</v>
@@ -6487,10 +6487,10 @@
         <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.017408</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.019061</v>
       </c>
       <c r="F100" s="3" t="n">
         <v>0</v>
@@ -42785,7 +42785,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr"/>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E340" t="inlineStr">
         <is>
           <t>-</t>
@@ -60599,7 +60603,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D518" t="inlineStr"/>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E518" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MN.xlsx
+++ b/output/pdf_financials_xlsx/MN.xlsx
@@ -807,10 +807,10 @@
         <v>0.400646</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.005903</v>
+        <v>0.463734</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.008976</v>
+        <v>0.5179280000000001</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0.381542</v>
@@ -1398,10 +1398,10 @@
         <v>-2.833259</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>-2.284301</v>
+        <v>-2.292931</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>-1.566113</v>
+        <v>-1.722083</v>
       </c>
     </row>
     <row r="17">
@@ -1456,10 +1456,10 @@
         <v>-0</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>-0</v>
+        <v>0.008630000000000001</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>-0</v>
+        <v>0.15597</v>
       </c>
     </row>
     <row r="18">
@@ -2200,10 +2200,10 @@
         <v>-2.833259</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-2.284301</v>
+        <v>-2.292931</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-1.566113</v>
+        <v>-1.722083</v>
       </c>
     </row>
     <row r="28">
@@ -2324,10 +2324,10 @@
         <v>-2.833259</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-2.284301</v>
+        <v>-2.292931</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-1.566113</v>
+        <v>-1.722083</v>
       </c>
     </row>
     <row r="30">
@@ -2482,10 +2482,10 @@
         <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.3763741691311252</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-0</v>
+        <v>-9.057054741263922</v>
       </c>
     </row>
     <row r="32">
@@ -2945,16 +2945,16 @@
         <v>0</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>0.005315</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>0.003949</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.026257</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.014242</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>0</v>
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>0.00045</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>0</v>
@@ -3006,13 +3006,13 @@
         <v>0.001353</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0</v>
+        <v>0.003949</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0</v>
+        <v>0.026257</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0</v>
+        <v>0.014242</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>0</v>
@@ -3021,7 +3021,7 @@
         <v>0</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0</v>
+        <v>0.00045</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>0</v>
@@ -3412,13 +3412,13 @@
         <v>0.02856</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.150147</v>
+        <v>0.146198</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.249347</v>
+        <v>0.22309</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.110822</v>
+        <v>0.09658</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.015893</v>
@@ -4375,25 +4375,25 @@
         <v>0</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.033385</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.038682</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.012493</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.265981</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.344586</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>1.08373</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>1.043225</v>
       </c>
       <c r="J64" s="3" t="n">
         <v>0.0008899999999999999</v>
@@ -4414,13 +4414,13 @@
         <v>0</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>0.01044</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>0.002768</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>0</v>
+        <v>0.039661</v>
       </c>
     </row>
     <row r="65">
@@ -4549,19 +4549,19 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.173964</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.162386</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.133912</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.541871</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.753366</v>
       </c>
       <c r="H67" s="3" t="n">
         <v>0</v>
@@ -4588,13 +4588,13 @@
         <v>0</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.09641</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.0205</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>0.0378</v>
       </c>
     </row>
     <row r="68">
@@ -7131,7 +7131,7 @@
         <v>-0.030054</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.030712</v>
       </c>
       <c r="G111" s="3" t="n">
         <v>0</v>
@@ -8513,7 +8513,7 @@
         <v>-0.030054</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.030712</v>
       </c>
       <c r="G134" s="3" t="n">
         <v>0</v>
@@ -8571,7 +8571,7 @@
         <v>-3.176138</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-1.85237</v>
+        <v>-1.883082</v>
       </c>
       <c r="G135" s="3" t="n">
         <v>-0.302497</v>
@@ -32138,7 +32138,11 @@
           <t>Deposit on private placement</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -39224,7 +39228,11 @@
           <t>Deferred income taxes recovered</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr"/>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr">
         <is>
           <t>-</t>
@@ -39832,7 +39840,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr"/>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
           <t>-</t>
@@ -41159,7 +41171,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>-</t>
@@ -47716,7 +47732,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D389" t="inlineStr"/>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr">
         <is>
           <t>-</t>
@@ -56870,7 +56890,11 @@
           <t>Professional, consulting and director fees (note 14)</t>
         </is>
       </c>
-      <c r="D481" t="inlineStr"/>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E481" t="inlineStr">
         <is>
           <t>-</t>
